--- a/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_387_R41.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_387_R41.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4877</v>
+        <v>2.1949</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1826</v>
+        <v>1.3443</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3051</v>
+        <v>0.8506</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.261</v>
+        <v>0.6921</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1208</v>
+        <v>0.6747</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3817</v>
+        <v>0.0173</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4703</v>
+        <v>0.3439</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9797</v>
+        <v>0.671</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5093</v>
+        <v>-0.3271</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7313</v>
+        <v>0.3482</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8589</v>
+        <v>0.0037</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1276</v>
+        <v>0.3445</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8198</v>
+        <v>0.9099</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8198</v>
+        <v>0.9099</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0872</v>
+        <v>0.0479</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7123</v>
+        <v>-0.0897</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.625</v>
+        <v>0.1375</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1583</v>
+        <v>0.5451</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.0901</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1583</v>
+        <v>-0.5451</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3242</v>
+        <v>2.0979</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5059</v>
+        <v>1.4373</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8183</v>
+        <v>0.6606</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6921</v>
+        <v>-0.261</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6747</v>
+        <v>0.1208</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0173</v>
+        <v>-0.3817</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3439</v>
+        <v>0.4703</v>
       </c>
       <c r="K3" t="n">
-        <v>0.671</v>
+        <v>0.9797</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3271</v>
+        <v>-0.5093</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3482</v>
+        <v>-0.7313</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0037</v>
+        <v>-0.8589</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3445</v>
+        <v>0.1276</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9099</v>
+        <v>1.8198</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9099</v>
+        <v>1.8198</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1772</v>
+        <v>0.6974</v>
       </c>
       <c r="T3" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.9669</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1052</v>
+        <v>-0.2695</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5451</v>
+        <v>-0.1583</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0901</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5451</v>
+        <v>-0.1583</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2568</v>
+        <v>2.0305</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1988</v>
+        <v>1.0371</v>
       </c>
       <c r="F4" t="n">
-        <v>1.058</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>0.9743000000000001</v>
@@ -766,13 +766,13 @@
         <v>1.5923</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9386</v>
+        <v>0.7123</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8502</v>
+        <v>0.6886</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.0238</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2485</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9386</v>
+        <v>0.3172</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.1871</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3564</v>
+        <v>0.1301</v>
       </c>
       <c r="G5" t="n">
         <v>-0.634</v>
@@ -844,13 +844,13 @@
         <v>0.9099</v>
       </c>
       <c r="S5" t="n">
-        <v>1.7528</v>
+        <v>1.1314</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9819</v>
+        <v>0.5867</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7709</v>
+        <v>0.5447</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0901</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3714</v>
+        <v>0.1746</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.3328</v>
+        <v>-1.7222</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9614</v>
+        <v>1.8968</v>
       </c>
       <c r="G6" t="n">
         <v>1.5115</v>
@@ -922,13 +922,13 @@
         <v>1.5923</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1269</v>
+        <v>0.419</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0597</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0672</v>
+        <v>-0.1319</v>
       </c>
       <c r="V6" t="n">
         <v>2.3386</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4697</v>
+        <v>-0.5699</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7014</v>
+        <v>-1.6998</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2317</v>
+        <v>1.1299</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.2105</v>
+        <v>0.0457</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7591</v>
+        <v>1.867</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.4514</v>
+        <v>-1.8213</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2586</v>
+        <v>-0.3088</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6747</v>
+        <v>1.1732</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5838</v>
+        <v>-1.482</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9519</v>
+        <v>0.3545</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0844</v>
+        <v>0.6938</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8675</v>
+        <v>-0.3393</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2275</v>
+        <v>-1.5923</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1374</v>
+        <v>-2.2747</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9099</v>
+        <v>0.6824</v>
       </c>
       <c r="S7" t="n">
-        <v>1.9683</v>
+        <v>0.0449</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6946</v>
+        <v>-0.2064</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2737</v>
+        <v>0.2513</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.9318</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.0901</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1583</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1502</v>
+        <v>-0.651</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.346</v>
+        <v>0.1209</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8042</v>
+        <v>-0.7719</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7677</v>
@@ -1078,13 +1078,13 @@
         <v>0.6824</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3616</v>
+        <v>0.1377</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1197</v>
+        <v>0.3473</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2419</v>
+        <v>-0.2096</v>
       </c>
       <c r="V8" t="n">
         <v>-0.7034</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6133</v>
+        <v>-1.3986</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3553</v>
+        <v>-1.8327</v>
       </c>
       <c r="F9" t="n">
-        <v>0.742</v>
+        <v>0.434</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0457</v>
+        <v>-1.3627</v>
       </c>
       <c r="H9" t="n">
-        <v>1.867</v>
+        <v>0.5198</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.8213</v>
+        <v>-1.8825</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3088</v>
+        <v>-0.5158</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1732</v>
+        <v>0.9661</v>
       </c>
       <c r="L9" t="n">
         <v>-1.482</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3545</v>
+        <v>-0.8469</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6938</v>
+        <v>-0.4463</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3393</v>
+        <v>-0.4006</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5923</v>
+        <v>-0.2275</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2747</v>
+        <v>-1.1374</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6824</v>
+        <v>0.9099</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9985000000000001</v>
+        <v>0.1916</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8619</v>
+        <v>-0.1795</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1365</v>
+        <v>0.3711</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9318</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0901</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7279</v>
+        <v>-1.4748</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8159</v>
+        <v>-2.7889</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0879</v>
+        <v>1.3142</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8522</v>
@@ -1234,13 +1234,13 @@
         <v>1.5923</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5101</v>
+        <v>0.7633</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3474</v>
+        <v>0.3743</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1627</v>
+        <v>0.3889</v>
       </c>
       <c r="V10" t="n">
         <v>-0.7034</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7566</v>
+        <v>-1.531</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7539</v>
+        <v>-2.2132</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9973</v>
+        <v>0.6822</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7206</v>
+        <v>-2.2105</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0022</v>
+        <v>-0.7591</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.7228</v>
+        <v>-1.4514</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3412</v>
+        <v>-1.2586</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1035</v>
+        <v>-0.6747</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4447</v>
+        <v>-0.5838</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3794</v>
+        <v>-0.9519</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1013</v>
+        <v>-0.0844</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2781</v>
+        <v>-0.8675</v>
       </c>
       <c r="P11" t="n">
         <v>-0.2275</v>
@@ -1312,13 +1312,13 @@
         <v>0.9099</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1915</v>
+        <v>0.9069</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2753</v>
+        <v>0.1827</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4668</v>
+        <v>0.7242</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,40 +1345,40 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0595</v>
+        <v>-1.6128</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2996</v>
+        <v>-2.2869</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2401</v>
+        <v>0.6741</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.3627</v>
+        <v>-1.7206</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5198</v>
+        <v>0.0022</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8825</v>
+        <v>-1.7228</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5158</v>
+        <v>-1.3412</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9661</v>
+        <v>0.1035</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.482</v>
+        <v>-1.4447</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8469</v>
+        <v>-0.3794</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4463</v>
+        <v>-0.1013</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4006</v>
+        <v>-0.2781</v>
       </c>
       <c r="P12" t="n">
         <v>-0.2275</v>
@@ -1390,13 +1390,13 @@
         <v>0.9099</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4693</v>
+        <v>0.3352</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6464</v>
+        <v>0.1916</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1771</v>
+        <v>0.1436</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.141299999999999</v>
+        <v>-0.4230000000000003</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.135400000000001</v>
+        <v>-8.417000000000002</v>
       </c>
       <c r="F13" t="n">
         <v>7.994000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.585100000000001</v>
+        <v>-4.5851</v>
       </c>
       <c r="H13" t="n">
         <v>6.3101</v>
@@ -1441,13 +1441,13 @@
         <v>-10.8953</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.7011</v>
+        <v>-2.701099999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>7.1356</v>
+        <v>7.135600000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-9.836499999999997</v>
+        <v>-9.836500000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-1.8841</v>
@@ -1459,7 +1459,7 @@
         <v>-1.0586</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1374</v>
+        <v>-1.137399999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.6484</v>
@@ -1468,13 +1468,13 @@
         <v>12.511</v>
       </c>
       <c r="S13" t="n">
-        <v>4.6694</v>
+        <v>5.387600000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>2.6954</v>
+        <v>3.413399999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9742</v>
+        <v>1.9741</v>
       </c>
       <c r="V13" t="n">
         <v>-0.08819999999999983</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.521</v>
+        <v>3.4189</v>
       </c>
       <c r="E14" t="n">
-        <v>2.911</v>
+        <v>1.6269</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6099</v>
+        <v>1.792</v>
       </c>
       <c r="G14" t="n">
         <v>2.7102</v>
@@ -1546,13 +1546,13 @@
         <v>1.8198</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0392</v>
+        <v>-0.0629</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2573</v>
+        <v>-0.0268</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2181</v>
+        <v>-0.0361</v>
       </c>
       <c r="V14" t="n">
         <v>0.3167</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2177</v>
+        <v>2.628</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3421</v>
+        <v>1.7584</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8756</v>
+        <v>0.8696</v>
       </c>
       <c r="G15" t="n">
         <v>2.655</v>
@@ -1624,13 +1624,13 @@
         <v>1.3648</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5627</v>
+        <v>-0.027</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9939</v>
+        <v>0.4102</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4312</v>
+        <v>-0.4371</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2132</v>
+        <v>0.2652</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4522</v>
+        <v>-0.3355</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6654</v>
+        <v>0.6008</v>
       </c>
       <c r="G16" t="n">
         <v>0.4239</v>
@@ -1702,13 +1702,13 @@
         <v>0.2275</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4382</v>
+        <v>-0.3861</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2873</v>
+        <v>-0.1706</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1509</v>
+        <v>-0.2155</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. OSMAN</t>
+          <t>T. SHORTS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2279</v>
+        <v>0.2492</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2799</v>
+        <v>-0.7412</v>
       </c>
       <c r="F17" t="n">
-        <v>0.052</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1422</v>
+        <v>-2.7541</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8791</v>
+        <v>-3.1159</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7369</v>
+        <v>0.3618</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6961000000000001</v>
+        <v>-2.284</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5885</v>
+        <v>-1.6176</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1077</v>
+        <v>-0.6665</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5538999999999999</v>
+        <v>-0.4701</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2907</v>
+        <v>-1.4984</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8446</v>
+        <v>1.0283</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2275</v>
+        <v>1.5923</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1374</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9099</v>
+        <v>1.5923</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6186</v>
+        <v>-0.7692</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8502</v>
+        <v>-0.6374</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7684</v>
+        <v>-0.1318</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4768</v>
+        <v>2.1802</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7034</v>
+        <v>2.1802</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.1802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. GRIGONIS</t>
+          <t>J. GRANT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4797</v>
+        <v>0.1394</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5012</v>
+        <v>-2.4106</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0214</v>
+        <v>2.5501</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0096</v>
+        <v>-0.3215</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1196</v>
+        <v>-2.1239</v>
       </c>
       <c r="I18" t="n">
-        <v>0.89</v>
+        <v>1.8025</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2946</v>
+        <v>-0.9023</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8435</v>
+        <v>-1.6101</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4511</v>
+        <v>0.7078</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.285</v>
+        <v>0.5808</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7239</v>
+        <v>-0.5138</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4389</v>
+        <v>1.0947</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6824</v>
+        <v>0.9099</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.3648</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6824</v>
+        <v>2.2747</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-0.449</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.431</v>
+        <v>-0.1435</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.376</v>
+        <v>-0.3055</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. GRANT</t>
+          <t>M. GRIGONIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5274</v>
+        <v>-0.026</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4106</v>
+        <v>-0.2677</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8832</v>
+        <v>0.2417</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3215</v>
+        <v>1.0096</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.1239</v>
+        <v>0.1196</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8025</v>
+        <v>0.89</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9023</v>
+        <v>1.2946</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.6101</v>
+        <v>0.8435</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7078</v>
+        <v>0.4511</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5808</v>
+        <v>-0.285</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5138</v>
+        <v>-0.7239</v>
       </c>
       <c r="O19" t="n">
-        <v>1.0947</v>
+        <v>0.4389</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9099</v>
+        <v>-0.6824</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.3648</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2747</v>
+        <v>0.6824</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1158</v>
+        <v>-0.3532</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1435</v>
+        <v>-0.1975</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-0.1557</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. SHORTS</t>
+          <t>N. HAYES-DAVIS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6194</v>
+        <v>-0.768</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3249</v>
+        <v>-3.3599</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7055</v>
+        <v>2.592</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.7541</v>
+        <v>-0.2741</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.1159</v>
+        <v>-0.9819</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3618</v>
+        <v>0.7078</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.284</v>
+        <v>-0.3042</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.6176</v>
+        <v>0.2052</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6665</v>
+        <v>-0.5093</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4701</v>
+        <v>0.0301</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4984</v>
+        <v>-1.1871</v>
       </c>
       <c r="O20" t="n">
-        <v>1.0283</v>
+        <v>1.2171</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5923</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.2747</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5923</v>
+        <v>2.2747</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6378</v>
+        <v>-0.4939</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.221</v>
+        <v>-0.781</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4167</v>
+        <v>0.2872</v>
       </c>
       <c r="V20" t="n">
-        <v>2.1802</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1802</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9348</v>
+        <v>-0.8629</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.93</v>
+        <v>-0.6966</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0047</v>
+        <v>-0.1664</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6447000000000001</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1317</v>
+        <v>-0.0599</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2753</v>
+        <v>-0.0418</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1436</v>
+        <v>-0.018</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1583</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. HAYES-DAVIS</t>
+          <t>K. NUNN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5073</v>
+        <v>-1.0623</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9436</v>
+        <v>-2.5875</v>
       </c>
       <c r="F22" t="n">
-        <v>2.4363</v>
+        <v>1.5252</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2741</v>
+        <v>1.923</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9819</v>
+        <v>0.8784</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7078</v>
+        <v>1.0446</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3042</v>
+        <v>1.2709</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2052</v>
+        <v>2.0992</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5093</v>
+        <v>-0.8283</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0301</v>
+        <v>0.6521</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1871</v>
+        <v>-1.2208</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2171</v>
+        <v>1.8729</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2747</v>
+        <v>-3.6396</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2747</v>
+        <v>2.5022</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2332</v>
+        <v>-1.0745</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3647</v>
+        <v>-0.5356</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1315</v>
+        <v>-0.539</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.7734</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.3167</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K. NUNN</t>
+          <t>C. OSMAN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.514</v>
+        <v>-1.2839</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4047</v>
+        <v>-0.9802999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8907</v>
+        <v>-0.3035</v>
       </c>
       <c r="G23" t="n">
-        <v>1.923</v>
+        <v>-0.1422</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8784</v>
+        <v>-0.8791</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0446</v>
+        <v>0.7369</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2709</v>
+        <v>-0.6961000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>2.0992</v>
+        <v>-0.5885</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.8283</v>
+        <v>-0.1077</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6521</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2208</v>
+        <v>-0.2907</v>
       </c>
       <c r="O23" t="n">
-        <v>1.8729</v>
+        <v>0.8446</v>
       </c>
       <c r="P23" t="n">
+        <v>-0.2275</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-1.1374</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-3.6396</v>
-      </c>
       <c r="R23" t="n">
-        <v>2.5022</v>
+        <v>0.9099</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.5262</v>
+        <v>0.5627</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3527</v>
+        <v>0.1498</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1735</v>
+        <v>0.4129</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.7734</v>
+        <v>-1.4768</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3167</v>
+        <v>0.7034</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0901</v>
+        <v>-2.1802</v>
       </c>
     </row>
     <row r="24">
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.1414</v>
+        <v>2.6976</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.994000000000001</v>
+        <v>-7.994</v>
       </c>
       <c r="F24" t="n">
-        <v>9.135300000000001</v>
+        <v>10.6919</v>
       </c>
       <c r="G24" t="n">
-        <v>4.585099999999999</v>
+        <v>4.5851</v>
       </c>
       <c r="H24" t="n">
-        <v>-6.310199999999999</v>
+        <v>-6.3102</v>
       </c>
       <c r="I24" t="n">
         <v>10.8953</v>
@@ -2302,7 +2302,7 @@
         <v>1.8842</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8251000000000004</v>
+        <v>0.8250999999999997</v>
       </c>
       <c r="L24" t="n">
         <v>1.0587</v>
@@ -2311,10 +2311,10 @@
         <v>2.7009</v>
       </c>
       <c r="N24" t="n">
-        <v>-7.1357</v>
+        <v>-7.135700000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>9.836600000000001</v>
+        <v>9.836599999999999</v>
       </c>
       <c r="P24" t="n">
         <v>1.1373</v>
@@ -2326,16 +2326,16 @@
         <v>13.6483</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.6694</v>
+        <v>-3.113</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.9741</v>
+        <v>-1.9742</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.6952</v>
+        <v>-1.1386</v>
       </c>
       <c r="V24" t="n">
-        <v>0.08840000000000015</v>
+        <v>0.08840000000000003</v>
       </c>
       <c r="W24" t="n">
         <v>4.6071</v>
